--- a/output/2024_grupo_etario_por_comuna.xlsx
+++ b/output/2024_grupo_etario_por_comuna.xlsx
@@ -451,16 +451,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -476,7 +468,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -484,30 +476,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -806,276 +780,276 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:89">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>19</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" t="s">
         <v>20</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" t="s">
         <v>21</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" t="s">
         <v>22</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" t="s">
         <v>23</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AA1" t="s">
         <v>25</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AB1" t="s">
         <v>26</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AC1" t="s">
         <v>27</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AD1" t="s">
         <v>28</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AE1" t="s">
         <v>29</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AF1" t="s">
         <v>30</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AG1" t="s">
         <v>31</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AH1" t="s">
         <v>32</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AI1" t="s">
         <v>33</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AJ1" t="s">
         <v>34</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AK1" t="s">
         <v>35</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AL1" t="s">
         <v>36</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AM1" t="s">
         <v>37</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AN1" t="s">
         <v>38</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AO1" t="s">
         <v>39</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AP1" t="s">
         <v>40</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AQ1" t="s">
         <v>41</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AR1" t="s">
         <v>42</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AS1" t="s">
         <v>43</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AT1" t="s">
         <v>44</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AU1" t="s">
         <v>45</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AV1" t="s">
         <v>46</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AW1" t="s">
         <v>47</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="AX1" t="s">
         <v>48</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="AY1" t="s">
         <v>49</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="AZ1" t="s">
         <v>50</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="BA1" t="s">
         <v>51</v>
       </c>
-      <c r="BB1" s="1" t="s">
+      <c r="BB1" t="s">
         <v>52</v>
       </c>
-      <c r="BC1" s="1" t="s">
+      <c r="BC1" t="s">
         <v>53</v>
       </c>
-      <c r="BD1" s="1" t="s">
+      <c r="BD1" t="s">
         <v>54</v>
       </c>
-      <c r="BE1" s="1" t="s">
+      <c r="BE1" t="s">
         <v>55</v>
       </c>
-      <c r="BF1" s="1" t="s">
+      <c r="BF1" t="s">
         <v>56</v>
       </c>
-      <c r="BG1" s="1" t="s">
+      <c r="BG1" t="s">
         <v>57</v>
       </c>
-      <c r="BH1" s="1" t="s">
+      <c r="BH1" t="s">
         <v>58</v>
       </c>
-      <c r="BI1" s="1" t="s">
+      <c r="BI1" t="s">
         <v>59</v>
       </c>
-      <c r="BJ1" s="1" t="s">
+      <c r="BJ1" t="s">
         <v>60</v>
       </c>
-      <c r="BK1" s="1" t="s">
+      <c r="BK1" t="s">
         <v>61</v>
       </c>
-      <c r="BL1" s="1" t="s">
+      <c r="BL1" t="s">
         <v>62</v>
       </c>
-      <c r="BM1" s="1" t="s">
+      <c r="BM1" t="s">
         <v>63</v>
       </c>
-      <c r="BN1" s="1" t="s">
+      <c r="BN1" t="s">
         <v>64</v>
       </c>
-      <c r="BO1" s="1" t="s">
+      <c r="BO1" t="s">
         <v>65</v>
       </c>
-      <c r="BP1" s="1" t="s">
+      <c r="BP1" t="s">
         <v>66</v>
       </c>
-      <c r="BQ1" s="1" t="s">
+      <c r="BQ1" t="s">
         <v>67</v>
       </c>
-      <c r="BR1" s="1" t="s">
+      <c r="BR1" t="s">
         <v>68</v>
       </c>
-      <c r="BS1" s="1" t="s">
+      <c r="BS1" t="s">
         <v>69</v>
       </c>
-      <c r="BT1" s="1" t="s">
+      <c r="BT1" t="s">
         <v>70</v>
       </c>
-      <c r="BU1" s="1" t="s">
+      <c r="BU1" t="s">
         <v>71</v>
       </c>
-      <c r="BV1" s="1" t="s">
+      <c r="BV1" t="s">
         <v>72</v>
       </c>
-      <c r="BW1" s="1" t="s">
+      <c r="BW1" t="s">
         <v>73</v>
       </c>
-      <c r="BX1" s="1" t="s">
+      <c r="BX1" t="s">
         <v>74</v>
       </c>
-      <c r="BY1" s="1" t="s">
+      <c r="BY1" t="s">
         <v>75</v>
       </c>
-      <c r="BZ1" s="1" t="s">
+      <c r="BZ1" t="s">
         <v>76</v>
       </c>
-      <c r="CA1" s="1" t="s">
+      <c r="CA1" t="s">
         <v>77</v>
       </c>
-      <c r="CB1" s="1" t="s">
+      <c r="CB1" t="s">
         <v>78</v>
       </c>
-      <c r="CC1" s="1" t="s">
+      <c r="CC1" t="s">
         <v>79</v>
       </c>
-      <c r="CD1" s="1" t="s">
+      <c r="CD1" t="s">
         <v>80</v>
       </c>
-      <c r="CE1" s="1" t="s">
+      <c r="CE1" t="s">
         <v>81</v>
       </c>
-      <c r="CF1" s="1" t="s">
+      <c r="CF1" t="s">
         <v>82</v>
       </c>
-      <c r="CG1" s="1" t="s">
+      <c r="CG1" t="s">
         <v>83</v>
       </c>
-      <c r="CH1" s="1" t="s">
+      <c r="CH1" t="s">
         <v>84</v>
       </c>
-      <c r="CI1" s="1" t="s">
+      <c r="CI1" t="s">
         <v>85</v>
       </c>
-      <c r="CJ1" s="1" t="s">
+      <c r="CJ1" t="s">
         <v>86</v>
       </c>
-      <c r="CK1" s="1" t="s">
+      <c r="CK1" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:89">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>89</v>
       </c>
       <c r="B2">
@@ -1287,7 +1261,7 @@
       </c>
     </row>
     <row r="3" spans="1:89">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>90</v>
       </c>
       <c r="B3">
@@ -1511,7 +1485,7 @@
       </c>
     </row>
     <row r="4" spans="1:89">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>91</v>
       </c>
       <c r="B4">
@@ -1735,7 +1709,7 @@
       </c>
     </row>
     <row r="5" spans="1:89">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>92</v>
       </c>
       <c r="B5">
@@ -1959,7 +1933,7 @@
       </c>
     </row>
     <row r="6" spans="1:89">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>93</v>
       </c>
       <c r="B6">
@@ -2210,7 +2184,7 @@
       </c>
     </row>
     <row r="7" spans="1:89">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>94</v>
       </c>
       <c r="B7">
@@ -2461,7 +2435,7 @@
       </c>
     </row>
     <row r="8" spans="1:89">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>95</v>
       </c>
       <c r="B8">
@@ -2712,7 +2686,7 @@
       </c>
     </row>
     <row r="9" spans="1:89">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>96</v>
       </c>
       <c r="B9">
@@ -2930,7 +2904,7 @@
       </c>
     </row>
     <row r="10" spans="1:89">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>97</v>
       </c>
       <c r="B10">
@@ -3181,7 +3155,7 @@
       </c>
     </row>
     <row r="11" spans="1:89">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>98</v>
       </c>
       <c r="B11">
@@ -3408,7 +3382,7 @@
       </c>
     </row>
     <row r="12" spans="1:89">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>99</v>
       </c>
       <c r="B12">
@@ -3653,7 +3627,7 @@
       </c>
     </row>
     <row r="13" spans="1:89">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>100</v>
       </c>
       <c r="B13">
@@ -3904,7 +3878,7 @@
       </c>
     </row>
     <row r="14" spans="1:89">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>101</v>
       </c>
       <c r="B14">
@@ -4155,7 +4129,7 @@
       </c>
     </row>
     <row r="15" spans="1:89">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>102</v>
       </c>
       <c r="B15">
@@ -4373,7 +4347,7 @@
       </c>
     </row>
     <row r="16" spans="1:89">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>103</v>
       </c>
       <c r="B16">
@@ -4624,7 +4598,7 @@
       </c>
     </row>
     <row r="17" spans="1:89">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>104</v>
       </c>
       <c r="B17">
@@ -4875,7 +4849,7 @@
       </c>
     </row>
     <row r="18" spans="1:89">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>105</v>
       </c>
       <c r="B18">
@@ -5120,7 +5094,7 @@
       </c>
     </row>
     <row r="19" spans="1:89">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>106</v>
       </c>
       <c r="B19">
@@ -5359,7 +5333,7 @@
       </c>
     </row>
     <row r="20" spans="1:89">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>107</v>
       </c>
       <c r="B20">
@@ -5604,7 +5578,7 @@
       </c>
     </row>
     <row r="21" spans="1:89">
-      <c r="A21" s="1" t="s">
+      <c r="A21" t="s">
         <v>108</v>
       </c>
       <c r="B21">
@@ -5849,7 +5823,7 @@
       </c>
     </row>
     <row r="22" spans="1:89">
-      <c r="A22" s="1" t="s">
+      <c r="A22" t="s">
         <v>109</v>
       </c>
       <c r="B22">
@@ -6100,7 +6074,7 @@
       </c>
     </row>
     <row r="23" spans="1:89">
-      <c r="A23" s="1" t="s">
+      <c r="A23" t="s">
         <v>110</v>
       </c>
       <c r="B23">
@@ -6345,7 +6319,7 @@
       </c>
     </row>
     <row r="24" spans="1:89">
-      <c r="A24" s="1" t="s">
+      <c r="A24" t="s">
         <v>111</v>
       </c>
       <c r="B24">
@@ -6596,7 +6570,7 @@
       </c>
     </row>
     <row r="25" spans="1:89">
-      <c r="A25" s="1" t="s">
+      <c r="A25" t="s">
         <v>112</v>
       </c>
       <c r="B25">
@@ -6847,7 +6821,7 @@
       </c>
     </row>
     <row r="26" spans="1:89">
-      <c r="A26" s="1" t="s">
+      <c r="A26" t="s">
         <v>113</v>
       </c>
       <c r="B26">
@@ -7098,7 +7072,7 @@
       </c>
     </row>
     <row r="27" spans="1:89">
-      <c r="A27" s="1" t="s">
+      <c r="A27" t="s">
         <v>114</v>
       </c>
       <c r="B27">
@@ -7343,7 +7317,7 @@
       </c>
     </row>
     <row r="28" spans="1:89">
-      <c r="A28" s="1" t="s">
+      <c r="A28" t="s">
         <v>115</v>
       </c>
       <c r="B28">
@@ -7561,7 +7535,7 @@
       </c>
     </row>
     <row r="29" spans="1:89">
-      <c r="A29" s="1" t="s">
+      <c r="A29" t="s">
         <v>116</v>
       </c>
       <c r="B29">
@@ -7812,7 +7786,7 @@
       </c>
     </row>
     <row r="30" spans="1:89">
-      <c r="A30" s="1" t="s">
+      <c r="A30" t="s">
         <v>117</v>
       </c>
       <c r="B30">
@@ -8057,7 +8031,7 @@
       </c>
     </row>
     <row r="31" spans="1:89">
-      <c r="A31" s="1" t="s">
+      <c r="A31" t="s">
         <v>118</v>
       </c>
       <c r="B31">
@@ -8302,7 +8276,7 @@
       </c>
     </row>
     <row r="32" spans="1:89">
-      <c r="A32" s="1" t="s">
+      <c r="A32" t="s">
         <v>119</v>
       </c>
       <c r="B32">
@@ -8535,7 +8509,7 @@
       </c>
     </row>
     <row r="33" spans="1:89">
-      <c r="A33" s="1" t="s">
+      <c r="A33" t="s">
         <v>120</v>
       </c>
       <c r="B33">
@@ -8774,7 +8748,7 @@
       </c>
     </row>
     <row r="34" spans="1:89">
-      <c r="A34" s="1" t="s">
+      <c r="A34" t="s">
         <v>121</v>
       </c>
       <c r="B34">
@@ -9025,7 +8999,7 @@
       </c>
     </row>
     <row r="35" spans="1:89">
-      <c r="A35" s="1" t="s">
+      <c r="A35" t="s">
         <v>122</v>
       </c>
       <c r="B35">
@@ -9264,7 +9238,7 @@
       </c>
     </row>
     <row r="36" spans="1:89">
-      <c r="A36" s="1" t="s">
+      <c r="A36" t="s">
         <v>123</v>
       </c>
       <c r="B36">
@@ -9509,7 +9483,7 @@
       </c>
     </row>
     <row r="37" spans="1:89">
-      <c r="A37" s="1" t="s">
+      <c r="A37" t="s">
         <v>124</v>
       </c>
       <c r="B37">
@@ -9754,7 +9728,7 @@
       </c>
     </row>
     <row r="38" spans="1:89">
-      <c r="A38" s="1" t="s">
+      <c r="A38" t="s">
         <v>125</v>
       </c>
       <c r="B38">
@@ -10005,7 +9979,7 @@
       </c>
     </row>
     <row r="39" spans="1:89">
-      <c r="A39" s="1" t="s">
+      <c r="A39" t="s">
         <v>126</v>
       </c>
       <c r="B39">
@@ -10238,7 +10212,7 @@
       </c>
     </row>
     <row r="40" spans="1:89">
-      <c r="A40" s="1" t="s">
+      <c r="A40" t="s">
         <v>127</v>
       </c>
       <c r="B40">
@@ -10477,7 +10451,7 @@
       </c>
     </row>
     <row r="41" spans="1:89">
-      <c r="A41" s="1" t="s">
+      <c r="A41" t="s">
         <v>128</v>
       </c>
       <c r="B41">
@@ -10728,7 +10702,7 @@
       </c>
     </row>
     <row r="42" spans="1:89">
-      <c r="A42" s="1" t="s">
+      <c r="A42" t="s">
         <v>129</v>
       </c>
       <c r="B42">
@@ -10979,7 +10953,7 @@
       </c>
     </row>
     <row r="43" spans="1:89">
-      <c r="A43" s="1" t="s">
+      <c r="A43" t="s">
         <v>130</v>
       </c>
       <c r="B43">
@@ -11224,7 +11198,7 @@
       </c>
     </row>
     <row r="44" spans="1:89">
-      <c r="A44" s="1" t="s">
+      <c r="A44" t="s">
         <v>131</v>
       </c>
       <c r="B44">
@@ -11475,7 +11449,7 @@
       </c>
     </row>
     <row r="45" spans="1:89">
-      <c r="A45" s="1" t="s">
+      <c r="A45" t="s">
         <v>132</v>
       </c>
       <c r="B45">
@@ -11687,7 +11661,7 @@
       </c>
     </row>
     <row r="46" spans="1:89">
-      <c r="A46" s="1" t="s">
+      <c r="A46" t="s">
         <v>133</v>
       </c>
       <c r="B46">
@@ -11938,7 +11912,7 @@
       </c>
     </row>
     <row r="47" spans="1:89">
-      <c r="A47" s="1" t="s">
+      <c r="A47" t="s">
         <v>134</v>
       </c>
       <c r="B47">
@@ -12150,7 +12124,7 @@
       </c>
     </row>
     <row r="48" spans="1:89">
-      <c r="A48" s="1" t="s">
+      <c r="A48" t="s">
         <v>135</v>
       </c>
       <c r="B48">
@@ -12401,7 +12375,7 @@
       </c>
     </row>
     <row r="49" spans="1:89">
-      <c r="A49" s="1" t="s">
+      <c r="A49" t="s">
         <v>136</v>
       </c>
       <c r="B49">
@@ -12652,7 +12626,7 @@
       </c>
     </row>
     <row r="50" spans="1:89">
-      <c r="A50" s="1" t="s">
+      <c r="A50" t="s">
         <v>137</v>
       </c>
       <c r="B50">
@@ -12870,7 +12844,7 @@
       </c>
     </row>
     <row r="51" spans="1:89">
-      <c r="A51" s="1" t="s">
+      <c r="A51" t="s">
         <v>138</v>
       </c>
       <c r="B51">
@@ -13109,7 +13083,7 @@
       </c>
     </row>
     <row r="52" spans="1:89">
-      <c r="A52" s="1" t="s">
+      <c r="A52" t="s">
         <v>139</v>
       </c>
       <c r="B52">
@@ -13318,7 +13292,7 @@
       </c>
     </row>
     <row r="53" spans="1:89">
-      <c r="A53" s="1" t="s">
+      <c r="A53" t="s">
         <v>140</v>
       </c>
       <c r="B53">
@@ -13573,45 +13547,45 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>40</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>48</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>49</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>50</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>51</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>89</v>
       </c>
       <c r="B2">
@@ -13649,7 +13623,7 @@
       </c>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>90</v>
       </c>
       <c r="B3">
@@ -13687,7 +13661,7 @@
       </c>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>91</v>
       </c>
       <c r="B4">
@@ -13725,7 +13699,7 @@
       </c>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>92</v>
       </c>
       <c r="B5">
@@ -13763,7 +13737,7 @@
       </c>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>93</v>
       </c>
       <c r="B6">
@@ -13801,7 +13775,7 @@
       </c>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>94</v>
       </c>
       <c r="B7">
@@ -13839,7 +13813,7 @@
       </c>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>95</v>
       </c>
       <c r="B8">
@@ -13877,7 +13851,7 @@
       </c>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>96</v>
       </c>
       <c r="B9">
@@ -13915,7 +13889,7 @@
       </c>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>97</v>
       </c>
       <c r="B10">
@@ -13953,7 +13927,7 @@
       </c>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>98</v>
       </c>
       <c r="B11">
@@ -13991,7 +13965,7 @@
       </c>
     </row>
     <row r="12" spans="1:12">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>99</v>
       </c>
       <c r="B12">
@@ -14029,7 +14003,7 @@
       </c>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>100</v>
       </c>
       <c r="B13">
@@ -14067,7 +14041,7 @@
       </c>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>101</v>
       </c>
       <c r="B14">
@@ -14105,7 +14079,7 @@
       </c>
     </row>
     <row r="15" spans="1:12">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>102</v>
       </c>
       <c r="B15">
@@ -14143,7 +14117,7 @@
       </c>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>103</v>
       </c>
       <c r="B16">
@@ -14181,7 +14155,7 @@
       </c>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>104</v>
       </c>
       <c r="B17">
@@ -14219,7 +14193,7 @@
       </c>
     </row>
     <row r="18" spans="1:12">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>105</v>
       </c>
       <c r="B18">
@@ -14257,7 +14231,7 @@
       </c>
     </row>
     <row r="19" spans="1:12">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>106</v>
       </c>
       <c r="B19">
@@ -14295,7 +14269,7 @@
       </c>
     </row>
     <row r="20" spans="1:12">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>107</v>
       </c>
       <c r="B20">
@@ -14333,7 +14307,7 @@
       </c>
     </row>
     <row r="21" spans="1:12">
-      <c r="A21" s="1" t="s">
+      <c r="A21" t="s">
         <v>108</v>
       </c>
       <c r="B21">
@@ -14371,7 +14345,7 @@
       </c>
     </row>
     <row r="22" spans="1:12">
-      <c r="A22" s="1" t="s">
+      <c r="A22" t="s">
         <v>109</v>
       </c>
       <c r="B22">
@@ -14409,7 +14383,7 @@
       </c>
     </row>
     <row r="23" spans="1:12">
-      <c r="A23" s="1" t="s">
+      <c r="A23" t="s">
         <v>110</v>
       </c>
       <c r="B23">
@@ -14447,7 +14421,7 @@
       </c>
     </row>
     <row r="24" spans="1:12">
-      <c r="A24" s="1" t="s">
+      <c r="A24" t="s">
         <v>111</v>
       </c>
       <c r="B24">
@@ -14485,7 +14459,7 @@
       </c>
     </row>
     <row r="25" spans="1:12">
-      <c r="A25" s="1" t="s">
+      <c r="A25" t="s">
         <v>112</v>
       </c>
       <c r="B25">
@@ -14523,7 +14497,7 @@
       </c>
     </row>
     <row r="26" spans="1:12">
-      <c r="A26" s="1" t="s">
+      <c r="A26" t="s">
         <v>113</v>
       </c>
       <c r="B26">
@@ -14561,7 +14535,7 @@
       </c>
     </row>
     <row r="27" spans="1:12">
-      <c r="A27" s="1" t="s">
+      <c r="A27" t="s">
         <v>114</v>
       </c>
       <c r="B27">
@@ -14599,7 +14573,7 @@
       </c>
     </row>
     <row r="28" spans="1:12">
-      <c r="A28" s="1" t="s">
+      <c r="A28" t="s">
         <v>115</v>
       </c>
       <c r="B28">
@@ -14637,7 +14611,7 @@
       </c>
     </row>
     <row r="29" spans="1:12">
-      <c r="A29" s="1" t="s">
+      <c r="A29" t="s">
         <v>116</v>
       </c>
       <c r="B29">
@@ -14675,7 +14649,7 @@
       </c>
     </row>
     <row r="30" spans="1:12">
-      <c r="A30" s="1" t="s">
+      <c r="A30" t="s">
         <v>117</v>
       </c>
       <c r="B30">
@@ -14713,7 +14687,7 @@
       </c>
     </row>
     <row r="31" spans="1:12">
-      <c r="A31" s="1" t="s">
+      <c r="A31" t="s">
         <v>118</v>
       </c>
       <c r="B31">
@@ -14751,7 +14725,7 @@
       </c>
     </row>
     <row r="32" spans="1:12">
-      <c r="A32" s="1" t="s">
+      <c r="A32" t="s">
         <v>119</v>
       </c>
       <c r="B32">
@@ -14789,7 +14763,7 @@
       </c>
     </row>
     <row r="33" spans="1:12">
-      <c r="A33" s="1" t="s">
+      <c r="A33" t="s">
         <v>120</v>
       </c>
       <c r="B33">
@@ -14827,7 +14801,7 @@
       </c>
     </row>
     <row r="34" spans="1:12">
-      <c r="A34" s="1" t="s">
+      <c r="A34" t="s">
         <v>121</v>
       </c>
       <c r="B34">
@@ -14865,7 +14839,7 @@
       </c>
     </row>
     <row r="35" spans="1:12">
-      <c r="A35" s="1" t="s">
+      <c r="A35" t="s">
         <v>122</v>
       </c>
       <c r="B35">
@@ -14903,7 +14877,7 @@
       </c>
     </row>
     <row r="36" spans="1:12">
-      <c r="A36" s="1" t="s">
+      <c r="A36" t="s">
         <v>123</v>
       </c>
       <c r="B36">
@@ -14941,7 +14915,7 @@
       </c>
     </row>
     <row r="37" spans="1:12">
-      <c r="A37" s="1" t="s">
+      <c r="A37" t="s">
         <v>124</v>
       </c>
       <c r="B37">
@@ -14979,7 +14953,7 @@
       </c>
     </row>
     <row r="38" spans="1:12">
-      <c r="A38" s="1" t="s">
+      <c r="A38" t="s">
         <v>125</v>
       </c>
       <c r="B38">
@@ -15017,7 +14991,7 @@
       </c>
     </row>
     <row r="39" spans="1:12">
-      <c r="A39" s="1" t="s">
+      <c r="A39" t="s">
         <v>126</v>
       </c>
       <c r="B39">
@@ -15055,7 +15029,7 @@
       </c>
     </row>
     <row r="40" spans="1:12">
-      <c r="A40" s="1" t="s">
+      <c r="A40" t="s">
         <v>127</v>
       </c>
       <c r="B40">
@@ -15093,7 +15067,7 @@
       </c>
     </row>
     <row r="41" spans="1:12">
-      <c r="A41" s="1" t="s">
+      <c r="A41" t="s">
         <v>128</v>
       </c>
       <c r="B41">
@@ -15131,7 +15105,7 @@
       </c>
     </row>
     <row r="42" spans="1:12">
-      <c r="A42" s="1" t="s">
+      <c r="A42" t="s">
         <v>129</v>
       </c>
       <c r="B42">
@@ -15169,7 +15143,7 @@
       </c>
     </row>
     <row r="43" spans="1:12">
-      <c r="A43" s="1" t="s">
+      <c r="A43" t="s">
         <v>130</v>
       </c>
       <c r="B43">
@@ -15207,7 +15181,7 @@
       </c>
     </row>
     <row r="44" spans="1:12">
-      <c r="A44" s="1" t="s">
+      <c r="A44" t="s">
         <v>131</v>
       </c>
       <c r="B44">
@@ -15245,7 +15219,7 @@
       </c>
     </row>
     <row r="45" spans="1:12">
-      <c r="A45" s="1" t="s">
+      <c r="A45" t="s">
         <v>132</v>
       </c>
       <c r="B45">
@@ -15283,7 +15257,7 @@
       </c>
     </row>
     <row r="46" spans="1:12">
-      <c r="A46" s="1" t="s">
+      <c r="A46" t="s">
         <v>133</v>
       </c>
       <c r="B46">
@@ -15321,7 +15295,7 @@
       </c>
     </row>
     <row r="47" spans="1:12">
-      <c r="A47" s="1" t="s">
+      <c r="A47" t="s">
         <v>134</v>
       </c>
       <c r="B47">
@@ -15359,7 +15333,7 @@
       </c>
     </row>
     <row r="48" spans="1:12">
-      <c r="A48" s="1" t="s">
+      <c r="A48" t="s">
         <v>135</v>
       </c>
       <c r="B48">
@@ -15397,7 +15371,7 @@
       </c>
     </row>
     <row r="49" spans="1:12">
-      <c r="A49" s="1" t="s">
+      <c r="A49" t="s">
         <v>136</v>
       </c>
       <c r="B49">
@@ -15435,7 +15409,7 @@
       </c>
     </row>
     <row r="50" spans="1:12">
-      <c r="A50" s="1" t="s">
+      <c r="A50" t="s">
         <v>137</v>
       </c>
       <c r="B50">
@@ -15473,7 +15447,7 @@
       </c>
     </row>
     <row r="51" spans="1:12">
-      <c r="A51" s="1" t="s">
+      <c r="A51" t="s">
         <v>138</v>
       </c>
       <c r="B51">
@@ -15511,7 +15485,7 @@
       </c>
     </row>
     <row r="52" spans="1:12">
-      <c r="A52" s="1" t="s">
+      <c r="A52" t="s">
         <v>139</v>
       </c>
       <c r="B52">
@@ -15543,7 +15517,7 @@
       </c>
     </row>
     <row r="53" spans="1:12">
-      <c r="A53" s="1" t="s">
+      <c r="A53" t="s">
         <v>140</v>
       </c>
       <c r="B53">
@@ -15591,45 +15565,45 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>33</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>53</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>54</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>55</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>56</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>89</v>
       </c>
       <c r="B2">
@@ -15667,7 +15641,7 @@
       </c>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>90</v>
       </c>
       <c r="B3">
@@ -15705,7 +15679,7 @@
       </c>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>91</v>
       </c>
       <c r="B4">
@@ -15743,7 +15717,7 @@
       </c>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>92</v>
       </c>
       <c r="B5">
@@ -15781,7 +15755,7 @@
       </c>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>93</v>
       </c>
       <c r="B6">
@@ -15819,7 +15793,7 @@
       </c>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>94</v>
       </c>
       <c r="B7">
@@ -15857,7 +15831,7 @@
       </c>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>95</v>
       </c>
       <c r="B8">
@@ -15895,7 +15869,7 @@
       </c>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>96</v>
       </c>
       <c r="B9">
@@ -15933,7 +15907,7 @@
       </c>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>97</v>
       </c>
       <c r="B10">
@@ -15971,7 +15945,7 @@
       </c>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>98</v>
       </c>
       <c r="B11">
@@ -16009,7 +15983,7 @@
       </c>
     </row>
     <row r="12" spans="1:12">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>99</v>
       </c>
       <c r="B12">
@@ -16047,7 +16021,7 @@
       </c>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>100</v>
       </c>
       <c r="B13">
@@ -16085,7 +16059,7 @@
       </c>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>101</v>
       </c>
       <c r="B14">
@@ -16123,7 +16097,7 @@
       </c>
     </row>
     <row r="15" spans="1:12">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>102</v>
       </c>
       <c r="B15">
@@ -16161,7 +16135,7 @@
       </c>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>103</v>
       </c>
       <c r="B16">
@@ -16199,7 +16173,7 @@
       </c>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>104</v>
       </c>
       <c r="B17">
@@ -16237,7 +16211,7 @@
       </c>
     </row>
     <row r="18" spans="1:12">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>105</v>
       </c>
       <c r="B18">
@@ -16275,7 +16249,7 @@
       </c>
     </row>
     <row r="19" spans="1:12">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>106</v>
       </c>
       <c r="B19">
@@ -16313,7 +16287,7 @@
       </c>
     </row>
     <row r="20" spans="1:12">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>107</v>
       </c>
       <c r="B20">
@@ -16351,7 +16325,7 @@
       </c>
     </row>
     <row r="21" spans="1:12">
-      <c r="A21" s="1" t="s">
+      <c r="A21" t="s">
         <v>108</v>
       </c>
       <c r="B21">
@@ -16389,7 +16363,7 @@
       </c>
     </row>
     <row r="22" spans="1:12">
-      <c r="A22" s="1" t="s">
+      <c r="A22" t="s">
         <v>109</v>
       </c>
       <c r="B22">
@@ -16427,7 +16401,7 @@
       </c>
     </row>
     <row r="23" spans="1:12">
-      <c r="A23" s="1" t="s">
+      <c r="A23" t="s">
         <v>110</v>
       </c>
       <c r="B23">
@@ -16465,7 +16439,7 @@
       </c>
     </row>
     <row r="24" spans="1:12">
-      <c r="A24" s="1" t="s">
+      <c r="A24" t="s">
         <v>111</v>
       </c>
       <c r="B24">
@@ -16503,7 +16477,7 @@
       </c>
     </row>
     <row r="25" spans="1:12">
-      <c r="A25" s="1" t="s">
+      <c r="A25" t="s">
         <v>112</v>
       </c>
       <c r="B25">
@@ -16541,7 +16515,7 @@
       </c>
     </row>
     <row r="26" spans="1:12">
-      <c r="A26" s="1" t="s">
+      <c r="A26" t="s">
         <v>113</v>
       </c>
       <c r="B26">
@@ -16579,7 +16553,7 @@
       </c>
     </row>
     <row r="27" spans="1:12">
-      <c r="A27" s="1" t="s">
+      <c r="A27" t="s">
         <v>114</v>
       </c>
       <c r="B27">
@@ -16617,7 +16591,7 @@
       </c>
     </row>
     <row r="28" spans="1:12">
-      <c r="A28" s="1" t="s">
+      <c r="A28" t="s">
         <v>115</v>
       </c>
       <c r="B28">
@@ -16655,7 +16629,7 @@
       </c>
     </row>
     <row r="29" spans="1:12">
-      <c r="A29" s="1" t="s">
+      <c r="A29" t="s">
         <v>116</v>
       </c>
       <c r="B29">
@@ -16693,7 +16667,7 @@
       </c>
     </row>
     <row r="30" spans="1:12">
-      <c r="A30" s="1" t="s">
+      <c r="A30" t="s">
         <v>117</v>
       </c>
       <c r="B30">
@@ -16731,7 +16705,7 @@
       </c>
     </row>
     <row r="31" spans="1:12">
-      <c r="A31" s="1" t="s">
+      <c r="A31" t="s">
         <v>118</v>
       </c>
       <c r="B31">
@@ -16769,7 +16743,7 @@
       </c>
     </row>
     <row r="32" spans="1:12">
-      <c r="A32" s="1" t="s">
+      <c r="A32" t="s">
         <v>119</v>
       </c>
       <c r="B32">
@@ -16807,7 +16781,7 @@
       </c>
     </row>
     <row r="33" spans="1:12">
-      <c r="A33" s="1" t="s">
+      <c r="A33" t="s">
         <v>120</v>
       </c>
       <c r="B33">
@@ -16845,7 +16819,7 @@
       </c>
     </row>
     <row r="34" spans="1:12">
-      <c r="A34" s="1" t="s">
+      <c r="A34" t="s">
         <v>121</v>
       </c>
       <c r="B34">
@@ -16883,7 +16857,7 @@
       </c>
     </row>
     <row r="35" spans="1:12">
-      <c r="A35" s="1" t="s">
+      <c r="A35" t="s">
         <v>122</v>
       </c>
       <c r="B35">
@@ -16921,7 +16895,7 @@
       </c>
     </row>
     <row r="36" spans="1:12">
-      <c r="A36" s="1" t="s">
+      <c r="A36" t="s">
         <v>123</v>
       </c>
       <c r="B36">
@@ -16959,7 +16933,7 @@
       </c>
     </row>
     <row r="37" spans="1:12">
-      <c r="A37" s="1" t="s">
+      <c r="A37" t="s">
         <v>124</v>
       </c>
       <c r="B37">
@@ -16997,7 +16971,7 @@
       </c>
     </row>
     <row r="38" spans="1:12">
-      <c r="A38" s="1" t="s">
+      <c r="A38" t="s">
         <v>125</v>
       </c>
       <c r="B38">
@@ -17035,7 +17009,7 @@
       </c>
     </row>
     <row r="39" spans="1:12">
-      <c r="A39" s="1" t="s">
+      <c r="A39" t="s">
         <v>126</v>
       </c>
       <c r="B39">
@@ -17073,7 +17047,7 @@
       </c>
     </row>
     <row r="40" spans="1:12">
-      <c r="A40" s="1" t="s">
+      <c r="A40" t="s">
         <v>127</v>
       </c>
       <c r="B40">
@@ -17111,7 +17085,7 @@
       </c>
     </row>
     <row r="41" spans="1:12">
-      <c r="A41" s="1" t="s">
+      <c r="A41" t="s">
         <v>128</v>
       </c>
       <c r="B41">
@@ -17149,7 +17123,7 @@
       </c>
     </row>
     <row r="42" spans="1:12">
-      <c r="A42" s="1" t="s">
+      <c r="A42" t="s">
         <v>129</v>
       </c>
       <c r="B42">
@@ -17187,7 +17161,7 @@
       </c>
     </row>
     <row r="43" spans="1:12">
-      <c r="A43" s="1" t="s">
+      <c r="A43" t="s">
         <v>130</v>
       </c>
       <c r="B43">
@@ -17225,7 +17199,7 @@
       </c>
     </row>
     <row r="44" spans="1:12">
-      <c r="A44" s="1" t="s">
+      <c r="A44" t="s">
         <v>131</v>
       </c>
       <c r="B44">
@@ -17263,7 +17237,7 @@
       </c>
     </row>
     <row r="45" spans="1:12">
-      <c r="A45" s="1" t="s">
+      <c r="A45" t="s">
         <v>132</v>
       </c>
       <c r="B45">
@@ -17301,7 +17275,7 @@
       </c>
     </row>
     <row r="46" spans="1:12">
-      <c r="A46" s="1" t="s">
+      <c r="A46" t="s">
         <v>133</v>
       </c>
       <c r="B46">
@@ -17339,7 +17313,7 @@
       </c>
     </row>
     <row r="47" spans="1:12">
-      <c r="A47" s="1" t="s">
+      <c r="A47" t="s">
         <v>134</v>
       </c>
       <c r="B47">
@@ -17377,7 +17351,7 @@
       </c>
     </row>
     <row r="48" spans="1:12">
-      <c r="A48" s="1" t="s">
+      <c r="A48" t="s">
         <v>135</v>
       </c>
       <c r="B48">
@@ -17415,7 +17389,7 @@
       </c>
     </row>
     <row r="49" spans="1:12">
-      <c r="A49" s="1" t="s">
+      <c r="A49" t="s">
         <v>136</v>
       </c>
       <c r="B49">
@@ -17453,7 +17427,7 @@
       </c>
     </row>
     <row r="50" spans="1:12">
-      <c r="A50" s="1" t="s">
+      <c r="A50" t="s">
         <v>137</v>
       </c>
       <c r="B50">
@@ -17491,7 +17465,7 @@
       </c>
     </row>
     <row r="51" spans="1:12">
-      <c r="A51" s="1" t="s">
+      <c r="A51" t="s">
         <v>138</v>
       </c>
       <c r="B51">
@@ -17529,7 +17503,7 @@
       </c>
     </row>
     <row r="52" spans="1:12">
-      <c r="A52" s="1" t="s">
+      <c r="A52" t="s">
         <v>139</v>
       </c>
       <c r="B52">
@@ -17561,7 +17535,7 @@
       </c>
     </row>
     <row r="53" spans="1:12">
-      <c r="A53" s="1" t="s">
+      <c r="A53" t="s">
         <v>140</v>
       </c>
       <c r="B53">
@@ -17609,45 +17583,45 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>26</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>34</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>42</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>58</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>59</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>60</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>61</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>89</v>
       </c>
       <c r="B2">
@@ -17679,7 +17653,7 @@
       </c>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>90</v>
       </c>
       <c r="B3">
@@ -17717,7 +17691,7 @@
       </c>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>91</v>
       </c>
       <c r="B4">
@@ -17755,7 +17729,7 @@
       </c>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>92</v>
       </c>
       <c r="B5">
@@ -17793,7 +17767,7 @@
       </c>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>93</v>
       </c>
       <c r="B6">
@@ -17831,7 +17805,7 @@
       </c>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>94</v>
       </c>
       <c r="B7">
@@ -17869,7 +17843,7 @@
       </c>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>95</v>
       </c>
       <c r="B8">
@@ -17907,7 +17881,7 @@
       </c>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>96</v>
       </c>
       <c r="B9">
@@ -17945,7 +17919,7 @@
       </c>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>97</v>
       </c>
       <c r="B10">
@@ -17983,7 +17957,7 @@
       </c>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>98</v>
       </c>
       <c r="B11">
@@ -18015,7 +17989,7 @@
       </c>
     </row>
     <row r="12" spans="1:12">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>99</v>
       </c>
       <c r="B12">
@@ -18053,7 +18027,7 @@
       </c>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>100</v>
       </c>
       <c r="B13">
@@ -18091,7 +18065,7 @@
       </c>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>101</v>
       </c>
       <c r="B14">
@@ -18129,7 +18103,7 @@
       </c>
     </row>
     <row r="15" spans="1:12">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>102</v>
       </c>
       <c r="B15">
@@ -18167,7 +18141,7 @@
       </c>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>103</v>
       </c>
       <c r="B16">
@@ -18205,7 +18179,7 @@
       </c>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>104</v>
       </c>
       <c r="B17">
@@ -18243,7 +18217,7 @@
       </c>
     </row>
     <row r="18" spans="1:12">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>105</v>
       </c>
       <c r="B18">
@@ -18281,7 +18255,7 @@
       </c>
     </row>
     <row r="19" spans="1:12">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>106</v>
       </c>
       <c r="B19">
@@ -18319,7 +18293,7 @@
       </c>
     </row>
     <row r="20" spans="1:12">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>107</v>
       </c>
       <c r="B20">
@@ -18357,7 +18331,7 @@
       </c>
     </row>
     <row r="21" spans="1:12">
-      <c r="A21" s="1" t="s">
+      <c r="A21" t="s">
         <v>108</v>
       </c>
       <c r="B21">
@@ -18395,7 +18369,7 @@
       </c>
     </row>
     <row r="22" spans="1:12">
-      <c r="A22" s="1" t="s">
+      <c r="A22" t="s">
         <v>109</v>
       </c>
       <c r="B22">
@@ -18433,7 +18407,7 @@
       </c>
     </row>
     <row r="23" spans="1:12">
-      <c r="A23" s="1" t="s">
+      <c r="A23" t="s">
         <v>110</v>
       </c>
       <c r="B23">
@@ -18471,7 +18445,7 @@
       </c>
     </row>
     <row r="24" spans="1:12">
-      <c r="A24" s="1" t="s">
+      <c r="A24" t="s">
         <v>111</v>
       </c>
       <c r="B24">
@@ -18509,7 +18483,7 @@
       </c>
     </row>
     <row r="25" spans="1:12">
-      <c r="A25" s="1" t="s">
+      <c r="A25" t="s">
         <v>112</v>
       </c>
       <c r="B25">
@@ -18547,7 +18521,7 @@
       </c>
     </row>
     <row r="26" spans="1:12">
-      <c r="A26" s="1" t="s">
+      <c r="A26" t="s">
         <v>113</v>
       </c>
       <c r="B26">
@@ -18585,7 +18559,7 @@
       </c>
     </row>
     <row r="27" spans="1:12">
-      <c r="A27" s="1" t="s">
+      <c r="A27" t="s">
         <v>114</v>
       </c>
       <c r="B27">
@@ -18623,7 +18597,7 @@
       </c>
     </row>
     <row r="28" spans="1:12">
-      <c r="A28" s="1" t="s">
+      <c r="A28" t="s">
         <v>115</v>
       </c>
       <c r="B28">
@@ -18661,7 +18635,7 @@
       </c>
     </row>
     <row r="29" spans="1:12">
-      <c r="A29" s="1" t="s">
+      <c r="A29" t="s">
         <v>116</v>
       </c>
       <c r="B29">
@@ -18699,7 +18673,7 @@
       </c>
     </row>
     <row r="30" spans="1:12">
-      <c r="A30" s="1" t="s">
+      <c r="A30" t="s">
         <v>117</v>
       </c>
       <c r="B30">
@@ -18731,7 +18705,7 @@
       </c>
     </row>
     <row r="31" spans="1:12">
-      <c r="A31" s="1" t="s">
+      <c r="A31" t="s">
         <v>118</v>
       </c>
       <c r="B31">
@@ -18769,7 +18743,7 @@
       </c>
     </row>
     <row r="32" spans="1:12">
-      <c r="A32" s="1" t="s">
+      <c r="A32" t="s">
         <v>119</v>
       </c>
       <c r="B32">
@@ -18807,7 +18781,7 @@
       </c>
     </row>
     <row r="33" spans="1:12">
-      <c r="A33" s="1" t="s">
+      <c r="A33" t="s">
         <v>120</v>
       </c>
       <c r="B33">
@@ -18839,7 +18813,7 @@
       </c>
     </row>
     <row r="34" spans="1:12">
-      <c r="A34" s="1" t="s">
+      <c r="A34" t="s">
         <v>121</v>
       </c>
       <c r="B34">
@@ -18877,7 +18851,7 @@
       </c>
     </row>
     <row r="35" spans="1:12">
-      <c r="A35" s="1" t="s">
+      <c r="A35" t="s">
         <v>122</v>
       </c>
       <c r="B35">
@@ -18915,7 +18889,7 @@
       </c>
     </row>
     <row r="36" spans="1:12">
-      <c r="A36" s="1" t="s">
+      <c r="A36" t="s">
         <v>123</v>
       </c>
       <c r="B36">
@@ -18953,7 +18927,7 @@
       </c>
     </row>
     <row r="37" spans="1:12">
-      <c r="A37" s="1" t="s">
+      <c r="A37" t="s">
         <v>124</v>
       </c>
       <c r="B37">
@@ -18991,7 +18965,7 @@
       </c>
     </row>
     <row r="38" spans="1:12">
-      <c r="A38" s="1" t="s">
+      <c r="A38" t="s">
         <v>125</v>
       </c>
       <c r="B38">
@@ -19029,7 +19003,7 @@
       </c>
     </row>
     <row r="39" spans="1:12">
-      <c r="A39" s="1" t="s">
+      <c r="A39" t="s">
         <v>126</v>
       </c>
       <c r="B39">
@@ -19067,7 +19041,7 @@
       </c>
     </row>
     <row r="40" spans="1:12">
-      <c r="A40" s="1" t="s">
+      <c r="A40" t="s">
         <v>127</v>
       </c>
       <c r="B40">
@@ -19105,7 +19079,7 @@
       </c>
     </row>
     <row r="41" spans="1:12">
-      <c r="A41" s="1" t="s">
+      <c r="A41" t="s">
         <v>128</v>
       </c>
       <c r="B41">
@@ -19143,7 +19117,7 @@
       </c>
     </row>
     <row r="42" spans="1:12">
-      <c r="A42" s="1" t="s">
+      <c r="A42" t="s">
         <v>129</v>
       </c>
       <c r="B42">
@@ -19181,7 +19155,7 @@
       </c>
     </row>
     <row r="43" spans="1:12">
-      <c r="A43" s="1" t="s">
+      <c r="A43" t="s">
         <v>130</v>
       </c>
       <c r="B43">
@@ -19219,7 +19193,7 @@
       </c>
     </row>
     <row r="44" spans="1:12">
-      <c r="A44" s="1" t="s">
+      <c r="A44" t="s">
         <v>131</v>
       </c>
       <c r="B44">
@@ -19257,7 +19231,7 @@
       </c>
     </row>
     <row r="45" spans="1:12">
-      <c r="A45" s="1" t="s">
+      <c r="A45" t="s">
         <v>132</v>
       </c>
       <c r="B45">
@@ -19295,7 +19269,7 @@
       </c>
     </row>
     <row r="46" spans="1:12">
-      <c r="A46" s="1" t="s">
+      <c r="A46" t="s">
         <v>133</v>
       </c>
       <c r="B46">
@@ -19333,7 +19307,7 @@
       </c>
     </row>
     <row r="47" spans="1:12">
-      <c r="A47" s="1" t="s">
+      <c r="A47" t="s">
         <v>134</v>
       </c>
       <c r="B47">
@@ -19371,7 +19345,7 @@
       </c>
     </row>
     <row r="48" spans="1:12">
-      <c r="A48" s="1" t="s">
+      <c r="A48" t="s">
         <v>135</v>
       </c>
       <c r="B48">
@@ -19409,7 +19383,7 @@
       </c>
     </row>
     <row r="49" spans="1:12">
-      <c r="A49" s="1" t="s">
+      <c r="A49" t="s">
         <v>136</v>
       </c>
       <c r="B49">
@@ -19447,7 +19421,7 @@
       </c>
     </row>
     <row r="50" spans="1:12">
-      <c r="A50" s="1" t="s">
+      <c r="A50" t="s">
         <v>137</v>
       </c>
       <c r="B50">
@@ -19485,7 +19459,7 @@
       </c>
     </row>
     <row r="51" spans="1:12">
-      <c r="A51" s="1" t="s">
+      <c r="A51" t="s">
         <v>138</v>
       </c>
       <c r="B51">
@@ -19523,7 +19497,7 @@
       </c>
     </row>
     <row r="52" spans="1:12">
-      <c r="A52" s="1" t="s">
+      <c r="A52" t="s">
         <v>139</v>
       </c>
       <c r="B52">
@@ -19555,7 +19529,7 @@
       </c>
     </row>
     <row r="53" spans="1:12">
-      <c r="A53" s="1" t="s">
+      <c r="A53" t="s">
         <v>140</v>
       </c>
       <c r="B53">
@@ -19603,45 +19577,45 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>27</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>35</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>43</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>63</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>64</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>65</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>66</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>89</v>
       </c>
       <c r="B2">
@@ -19679,7 +19653,7 @@
       </c>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>90</v>
       </c>
       <c r="B3">
@@ -19717,7 +19691,7 @@
       </c>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>91</v>
       </c>
       <c r="B4">
@@ -19755,7 +19729,7 @@
       </c>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>92</v>
       </c>
       <c r="B5">
@@ -19793,7 +19767,7 @@
       </c>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>93</v>
       </c>
       <c r="B6">
@@ -19831,7 +19805,7 @@
       </c>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>94</v>
       </c>
       <c r="B7">
@@ -19869,7 +19843,7 @@
       </c>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>95</v>
       </c>
       <c r="B8">
@@ -19907,7 +19881,7 @@
       </c>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>96</v>
       </c>
       <c r="B9">
@@ -19945,7 +19919,7 @@
       </c>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>97</v>
       </c>
       <c r="B10">
@@ -19983,7 +19957,7 @@
       </c>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>98</v>
       </c>
       <c r="B11">
@@ -20021,7 +19995,7 @@
       </c>
     </row>
     <row r="12" spans="1:12">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>99</v>
       </c>
       <c r="B12">
@@ -20059,7 +20033,7 @@
       </c>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>100</v>
       </c>
       <c r="B13">
@@ -20097,7 +20071,7 @@
       </c>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>101</v>
       </c>
       <c r="B14">
@@ -20135,7 +20109,7 @@
       </c>
     </row>
     <row r="15" spans="1:12">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>102</v>
       </c>
       <c r="B15">
@@ -20173,7 +20147,7 @@
       </c>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>103</v>
       </c>
       <c r="B16">
@@ -20211,7 +20185,7 @@
       </c>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>104</v>
       </c>
       <c r="B17">
@@ -20249,7 +20223,7 @@
       </c>
     </row>
     <row r="18" spans="1:12">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>105</v>
       </c>
       <c r="B18">
@@ -20287,7 +20261,7 @@
       </c>
     </row>
     <row r="19" spans="1:12">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>106</v>
       </c>
       <c r="B19">
@@ -20325,7 +20299,7 @@
       </c>
     </row>
     <row r="20" spans="1:12">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>107</v>
       </c>
       <c r="B20">
@@ -20363,7 +20337,7 @@
       </c>
     </row>
     <row r="21" spans="1:12">
-      <c r="A21" s="1" t="s">
+      <c r="A21" t="s">
         <v>108</v>
       </c>
       <c r="B21">
@@ -20401,7 +20375,7 @@
       </c>
     </row>
     <row r="22" spans="1:12">
-      <c r="A22" s="1" t="s">
+      <c r="A22" t="s">
         <v>109</v>
       </c>
       <c r="B22">
@@ -20439,7 +20413,7 @@
       </c>
     </row>
     <row r="23" spans="1:12">
-      <c r="A23" s="1" t="s">
+      <c r="A23" t="s">
         <v>110</v>
       </c>
       <c r="B23">
@@ -20477,7 +20451,7 @@
       </c>
     </row>
     <row r="24" spans="1:12">
-      <c r="A24" s="1" t="s">
+      <c r="A24" t="s">
         <v>111</v>
       </c>
       <c r="B24">
@@ -20515,7 +20489,7 @@
       </c>
     </row>
     <row r="25" spans="1:12">
-      <c r="A25" s="1" t="s">
+      <c r="A25" t="s">
         <v>112</v>
       </c>
       <c r="B25">
@@ -20553,7 +20527,7 @@
       </c>
     </row>
     <row r="26" spans="1:12">
-      <c r="A26" s="1" t="s">
+      <c r="A26" t="s">
         <v>113</v>
       </c>
       <c r="B26">
@@ -20591,7 +20565,7 @@
       </c>
     </row>
     <row r="27" spans="1:12">
-      <c r="A27" s="1" t="s">
+      <c r="A27" t="s">
         <v>114</v>
       </c>
       <c r="B27">
@@ -20629,7 +20603,7 @@
       </c>
     </row>
     <row r="28" spans="1:12">
-      <c r="A28" s="1" t="s">
+      <c r="A28" t="s">
         <v>115</v>
       </c>
       <c r="B28">
@@ -20667,7 +20641,7 @@
       </c>
     </row>
     <row r="29" spans="1:12">
-      <c r="A29" s="1" t="s">
+      <c r="A29" t="s">
         <v>116</v>
       </c>
       <c r="B29">
@@ -20705,7 +20679,7 @@
       </c>
     </row>
     <row r="30" spans="1:12">
-      <c r="A30" s="1" t="s">
+      <c r="A30" t="s">
         <v>117</v>
       </c>
       <c r="B30">
@@ -20743,7 +20717,7 @@
       </c>
     </row>
     <row r="31" spans="1:12">
-      <c r="A31" s="1" t="s">
+      <c r="A31" t="s">
         <v>118</v>
       </c>
       <c r="B31">
@@ -20781,7 +20755,7 @@
       </c>
     </row>
     <row r="32" spans="1:12">
-      <c r="A32" s="1" t="s">
+      <c r="A32" t="s">
         <v>119</v>
       </c>
       <c r="B32">
@@ -20819,7 +20793,7 @@
       </c>
     </row>
     <row r="33" spans="1:12">
-      <c r="A33" s="1" t="s">
+      <c r="A33" t="s">
         <v>120</v>
       </c>
       <c r="B33">
@@ -20857,7 +20831,7 @@
       </c>
     </row>
     <row r="34" spans="1:12">
-      <c r="A34" s="1" t="s">
+      <c r="A34" t="s">
         <v>121</v>
       </c>
       <c r="B34">
@@ -20895,7 +20869,7 @@
       </c>
     </row>
     <row r="35" spans="1:12">
-      <c r="A35" s="1" t="s">
+      <c r="A35" t="s">
         <v>122</v>
       </c>
       <c r="B35">
@@ -20933,7 +20907,7 @@
       </c>
     </row>
     <row r="36" spans="1:12">
-      <c r="A36" s="1" t="s">
+      <c r="A36" t="s">
         <v>123</v>
       </c>
       <c r="B36">
@@ -20971,7 +20945,7 @@
       </c>
     </row>
     <row r="37" spans="1:12">
-      <c r="A37" s="1" t="s">
+      <c r="A37" t="s">
         <v>124</v>
       </c>
       <c r="B37">
@@ -21009,7 +20983,7 @@
       </c>
     </row>
     <row r="38" spans="1:12">
-      <c r="A38" s="1" t="s">
+      <c r="A38" t="s">
         <v>125</v>
       </c>
       <c r="B38">
@@ -21047,7 +21021,7 @@
       </c>
     </row>
     <row r="39" spans="1:12">
-      <c r="A39" s="1" t="s">
+      <c r="A39" t="s">
         <v>126</v>
       </c>
       <c r="B39">
@@ -21085,7 +21059,7 @@
       </c>
     </row>
     <row r="40" spans="1:12">
-      <c r="A40" s="1" t="s">
+      <c r="A40" t="s">
         <v>127</v>
       </c>
       <c r="B40">
@@ -21123,7 +21097,7 @@
       </c>
     </row>
     <row r="41" spans="1:12">
-      <c r="A41" s="1" t="s">
+      <c r="A41" t="s">
         <v>128</v>
       </c>
       <c r="B41">
@@ -21161,7 +21135,7 @@
       </c>
     </row>
     <row r="42" spans="1:12">
-      <c r="A42" s="1" t="s">
+      <c r="A42" t="s">
         <v>129</v>
       </c>
       <c r="B42">
@@ -21199,7 +21173,7 @@
       </c>
     </row>
     <row r="43" spans="1:12">
-      <c r="A43" s="1" t="s">
+      <c r="A43" t="s">
         <v>130</v>
       </c>
       <c r="B43">
@@ -21237,7 +21211,7 @@
       </c>
     </row>
     <row r="44" spans="1:12">
-      <c r="A44" s="1" t="s">
+      <c r="A44" t="s">
         <v>131</v>
       </c>
       <c r="B44">
@@ -21275,7 +21249,7 @@
       </c>
     </row>
     <row r="45" spans="1:12">
-      <c r="A45" s="1" t="s">
+      <c r="A45" t="s">
         <v>132</v>
       </c>
       <c r="B45">
@@ -21313,7 +21287,7 @@
       </c>
     </row>
     <row r="46" spans="1:12">
-      <c r="A46" s="1" t="s">
+      <c r="A46" t="s">
         <v>133</v>
       </c>
       <c r="B46">
@@ -21351,7 +21325,7 @@
       </c>
     </row>
     <row r="47" spans="1:12">
-      <c r="A47" s="1" t="s">
+      <c r="A47" t="s">
         <v>134</v>
       </c>
       <c r="B47">
@@ -21389,7 +21363,7 @@
       </c>
     </row>
     <row r="48" spans="1:12">
-      <c r="A48" s="1" t="s">
+      <c r="A48" t="s">
         <v>135</v>
       </c>
       <c r="B48">
@@ -21427,7 +21401,7 @@
       </c>
     </row>
     <row r="49" spans="1:12">
-      <c r="A49" s="1" t="s">
+      <c r="A49" t="s">
         <v>136</v>
       </c>
       <c r="B49">
@@ -21465,7 +21439,7 @@
       </c>
     </row>
     <row r="50" spans="1:12">
-      <c r="A50" s="1" t="s">
+      <c r="A50" t="s">
         <v>137</v>
       </c>
       <c r="B50">
@@ -21503,7 +21477,7 @@
       </c>
     </row>
     <row r="51" spans="1:12">
-      <c r="A51" s="1" t="s">
+      <c r="A51" t="s">
         <v>138</v>
       </c>
       <c r="B51">
@@ -21541,7 +21515,7 @@
       </c>
     </row>
     <row r="52" spans="1:12">
-      <c r="A52" s="1" t="s">
+      <c r="A52" t="s">
         <v>139</v>
       </c>
       <c r="B52">
@@ -21573,7 +21547,7 @@
       </c>
     </row>
     <row r="53" spans="1:12">
-      <c r="A53" s="1" t="s">
+      <c r="A53" t="s">
         <v>140</v>
       </c>
       <c r="B53">
@@ -21621,45 +21595,45 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>28</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>36</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>44</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>68</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>69</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>70</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>71</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>89</v>
       </c>
       <c r="B2">
@@ -21691,7 +21665,7 @@
       </c>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>90</v>
       </c>
       <c r="B3">
@@ -21723,7 +21697,7 @@
       </c>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>91</v>
       </c>
       <c r="B4">
@@ -21755,7 +21729,7 @@
       </c>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>92</v>
       </c>
       <c r="B5">
@@ -21787,7 +21761,7 @@
       </c>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>93</v>
       </c>
       <c r="B6">
@@ -21819,7 +21793,7 @@
       </c>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>94</v>
       </c>
       <c r="B7">
@@ -21851,7 +21825,7 @@
       </c>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>95</v>
       </c>
       <c r="B8">
@@ -21883,7 +21857,7 @@
       </c>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>96</v>
       </c>
       <c r="B9">
@@ -21909,7 +21883,7 @@
       </c>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>97</v>
       </c>
       <c r="B10">
@@ -21941,7 +21915,7 @@
       </c>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>98</v>
       </c>
       <c r="B11">
@@ -21967,7 +21941,7 @@
       </c>
     </row>
     <row r="12" spans="1:12">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>99</v>
       </c>
       <c r="B12">
@@ -21999,7 +21973,7 @@
       </c>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>100</v>
       </c>
       <c r="B13">
@@ -22031,7 +22005,7 @@
       </c>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>101</v>
       </c>
       <c r="B14">
@@ -22063,7 +22037,7 @@
       </c>
     </row>
     <row r="15" spans="1:12">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>102</v>
       </c>
       <c r="B15">
@@ -22095,7 +22069,7 @@
       </c>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>103</v>
       </c>
       <c r="B16">
@@ -22127,7 +22101,7 @@
       </c>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>104</v>
       </c>
       <c r="B17">
@@ -22159,7 +22133,7 @@
       </c>
     </row>
     <row r="18" spans="1:12">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>105</v>
       </c>
       <c r="B18">
@@ -22191,7 +22165,7 @@
       </c>
     </row>
     <row r="19" spans="1:12">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>106</v>
       </c>
       <c r="B19">
@@ -22223,7 +22197,7 @@
       </c>
     </row>
     <row r="20" spans="1:12">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>107</v>
       </c>
       <c r="B20">
@@ -22255,7 +22229,7 @@
       </c>
     </row>
     <row r="21" spans="1:12">
-      <c r="A21" s="1" t="s">
+      <c r="A21" t="s">
         <v>108</v>
       </c>
       <c r="B21">
@@ -22287,7 +22261,7 @@
       </c>
     </row>
     <row r="22" spans="1:12">
-      <c r="A22" s="1" t="s">
+      <c r="A22" t="s">
         <v>109</v>
       </c>
       <c r="B22">
@@ -22319,7 +22293,7 @@
       </c>
     </row>
     <row r="23" spans="1:12">
-      <c r="A23" s="1" t="s">
+      <c r="A23" t="s">
         <v>110</v>
       </c>
       <c r="B23">
@@ -22345,7 +22319,7 @@
       </c>
     </row>
     <row r="24" spans="1:12">
-      <c r="A24" s="1" t="s">
+      <c r="A24" t="s">
         <v>111</v>
       </c>
       <c r="B24">
@@ -22377,7 +22351,7 @@
       </c>
     </row>
     <row r="25" spans="1:12">
-      <c r="A25" s="1" t="s">
+      <c r="A25" t="s">
         <v>112</v>
       </c>
       <c r="B25">
@@ -22409,7 +22383,7 @@
       </c>
     </row>
     <row r="26" spans="1:12">
-      <c r="A26" s="1" t="s">
+      <c r="A26" t="s">
         <v>113</v>
       </c>
       <c r="B26">
@@ -22441,7 +22415,7 @@
       </c>
     </row>
     <row r="27" spans="1:12">
-      <c r="A27" s="1" t="s">
+      <c r="A27" t="s">
         <v>114</v>
       </c>
       <c r="B27">
@@ -22473,7 +22447,7 @@
       </c>
     </row>
     <row r="28" spans="1:12">
-      <c r="A28" s="1" t="s">
+      <c r="A28" t="s">
         <v>115</v>
       </c>
       <c r="B28">
@@ -22505,7 +22479,7 @@
       </c>
     </row>
     <row r="29" spans="1:12">
-      <c r="A29" s="1" t="s">
+      <c r="A29" t="s">
         <v>116</v>
       </c>
       <c r="B29">
@@ -22537,7 +22511,7 @@
       </c>
     </row>
     <row r="30" spans="1:12">
-      <c r="A30" s="1" t="s">
+      <c r="A30" t="s">
         <v>117</v>
       </c>
       <c r="B30">
@@ -22569,7 +22543,7 @@
       </c>
     </row>
     <row r="31" spans="1:12">
-      <c r="A31" s="1" t="s">
+      <c r="A31" t="s">
         <v>118</v>
       </c>
       <c r="B31">
@@ -22601,7 +22575,7 @@
       </c>
     </row>
     <row r="32" spans="1:12">
-      <c r="A32" s="1" t="s">
+      <c r="A32" t="s">
         <v>119</v>
       </c>
       <c r="B32">
@@ -22633,7 +22607,7 @@
       </c>
     </row>
     <row r="33" spans="1:12">
-      <c r="A33" s="1" t="s">
+      <c r="A33" t="s">
         <v>120</v>
       </c>
       <c r="B33">
@@ -22665,7 +22639,7 @@
       </c>
     </row>
     <row r="34" spans="1:12">
-      <c r="A34" s="1" t="s">
+      <c r="A34" t="s">
         <v>121</v>
       </c>
       <c r="B34">
@@ -22697,7 +22671,7 @@
       </c>
     </row>
     <row r="35" spans="1:12">
-      <c r="A35" s="1" t="s">
+      <c r="A35" t="s">
         <v>122</v>
       </c>
       <c r="B35">
@@ -22729,7 +22703,7 @@
       </c>
     </row>
     <row r="36" spans="1:12">
-      <c r="A36" s="1" t="s">
+      <c r="A36" t="s">
         <v>123</v>
       </c>
       <c r="B36">
@@ -22761,7 +22735,7 @@
       </c>
     </row>
     <row r="37" spans="1:12">
-      <c r="A37" s="1" t="s">
+      <c r="A37" t="s">
         <v>124</v>
       </c>
       <c r="B37">
@@ -22793,7 +22767,7 @@
       </c>
     </row>
     <row r="38" spans="1:12">
-      <c r="A38" s="1" t="s">
+      <c r="A38" t="s">
         <v>125</v>
       </c>
       <c r="B38">
@@ -22825,7 +22799,7 @@
       </c>
     </row>
     <row r="39" spans="1:12">
-      <c r="A39" s="1" t="s">
+      <c r="A39" t="s">
         <v>126</v>
       </c>
       <c r="B39">
@@ -22857,7 +22831,7 @@
       </c>
     </row>
     <row r="40" spans="1:12">
-      <c r="A40" s="1" t="s">
+      <c r="A40" t="s">
         <v>127</v>
       </c>
       <c r="B40">
@@ -22889,7 +22863,7 @@
       </c>
     </row>
     <row r="41" spans="1:12">
-      <c r="A41" s="1" t="s">
+      <c r="A41" t="s">
         <v>128</v>
       </c>
       <c r="B41">
@@ -22921,7 +22895,7 @@
       </c>
     </row>
     <row r="42" spans="1:12">
-      <c r="A42" s="1" t="s">
+      <c r="A42" t="s">
         <v>129</v>
       </c>
       <c r="B42">
@@ -22953,7 +22927,7 @@
       </c>
     </row>
     <row r="43" spans="1:12">
-      <c r="A43" s="1" t="s">
+      <c r="A43" t="s">
         <v>130</v>
       </c>
       <c r="B43">
@@ -22985,7 +22959,7 @@
       </c>
     </row>
     <row r="44" spans="1:12">
-      <c r="A44" s="1" t="s">
+      <c r="A44" t="s">
         <v>131</v>
       </c>
       <c r="B44">
@@ -23017,7 +22991,7 @@
       </c>
     </row>
     <row r="45" spans="1:12">
-      <c r="A45" s="1" t="s">
+      <c r="A45" t="s">
         <v>132</v>
       </c>
       <c r="B45">
@@ -23043,7 +23017,7 @@
       </c>
     </row>
     <row r="46" spans="1:12">
-      <c r="A46" s="1" t="s">
+      <c r="A46" t="s">
         <v>133</v>
       </c>
       <c r="B46">
@@ -23075,7 +23049,7 @@
       </c>
     </row>
     <row r="47" spans="1:12">
-      <c r="A47" s="1" t="s">
+      <c r="A47" t="s">
         <v>134</v>
       </c>
       <c r="B47">
@@ -23101,7 +23075,7 @@
       </c>
     </row>
     <row r="48" spans="1:12">
-      <c r="A48" s="1" t="s">
+      <c r="A48" t="s">
         <v>135</v>
       </c>
       <c r="B48">
@@ -23133,7 +23107,7 @@
       </c>
     </row>
     <row r="49" spans="1:12">
-      <c r="A49" s="1" t="s">
+      <c r="A49" t="s">
         <v>136</v>
       </c>
       <c r="B49">
@@ -23165,7 +23139,7 @@
       </c>
     </row>
     <row r="50" spans="1:12">
-      <c r="A50" s="1" t="s">
+      <c r="A50" t="s">
         <v>137</v>
       </c>
       <c r="B50">
@@ -23197,7 +23171,7 @@
       </c>
     </row>
     <row r="51" spans="1:12">
-      <c r="A51" s="1" t="s">
+      <c r="A51" t="s">
         <v>138</v>
       </c>
       <c r="B51">
@@ -23223,7 +23197,7 @@
       </c>
     </row>
     <row r="52" spans="1:12">
-      <c r="A52" s="1" t="s">
+      <c r="A52" t="s">
         <v>139</v>
       </c>
       <c r="B52">
@@ -23249,7 +23223,7 @@
       </c>
     </row>
     <row r="53" spans="1:12">
-      <c r="A53" s="1" t="s">
+      <c r="A53" t="s">
         <v>140</v>
       </c>
       <c r="B53">
@@ -23291,65 +23265,65 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>29</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>45</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>73</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>74</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>75</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>76</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>93</v>
       </c>
       <c r="B6">
@@ -23381,7 +23355,7 @@
       </c>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>94</v>
       </c>
       <c r="B7">
@@ -23413,7 +23387,7 @@
       </c>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>95</v>
       </c>
       <c r="B8">
@@ -23445,12 +23419,12 @@
       </c>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>97</v>
       </c>
       <c r="B10">
@@ -23482,7 +23456,7 @@
       </c>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>98</v>
       </c>
       <c r="B11">
@@ -23502,7 +23476,7 @@
       </c>
     </row>
     <row r="12" spans="1:12">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>99</v>
       </c>
       <c r="B12">
@@ -23528,7 +23502,7 @@
       </c>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>100</v>
       </c>
       <c r="B13">
@@ -23560,7 +23534,7 @@
       </c>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>101</v>
       </c>
       <c r="B14">
@@ -23592,12 +23566,12 @@
       </c>
     </row>
     <row r="15" spans="1:12">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>103</v>
       </c>
       <c r="B16">
@@ -23629,7 +23603,7 @@
       </c>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>104</v>
       </c>
       <c r="B17">
@@ -23661,7 +23635,7 @@
       </c>
     </row>
     <row r="18" spans="1:12">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>105</v>
       </c>
       <c r="B18">
@@ -23687,7 +23661,7 @@
       </c>
     </row>
     <row r="19" spans="1:12">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>106</v>
       </c>
       <c r="B19">
@@ -23707,7 +23681,7 @@
       </c>
     </row>
     <row r="20" spans="1:12">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>107</v>
       </c>
       <c r="B20">
@@ -23733,7 +23707,7 @@
       </c>
     </row>
     <row r="21" spans="1:12">
-      <c r="A21" s="1" t="s">
+      <c r="A21" t="s">
         <v>108</v>
       </c>
       <c r="B21">
@@ -23759,7 +23733,7 @@
       </c>
     </row>
     <row r="22" spans="1:12">
-      <c r="A22" s="1" t="s">
+      <c r="A22" t="s">
         <v>109</v>
       </c>
       <c r="B22">
@@ -23791,7 +23765,7 @@
       </c>
     </row>
     <row r="23" spans="1:12">
-      <c r="A23" s="1" t="s">
+      <c r="A23" t="s">
         <v>110</v>
       </c>
       <c r="B23">
@@ -23823,7 +23797,7 @@
       </c>
     </row>
     <row r="24" spans="1:12">
-      <c r="A24" s="1" t="s">
+      <c r="A24" t="s">
         <v>111</v>
       </c>
       <c r="B24">
@@ -23855,7 +23829,7 @@
       </c>
     </row>
     <row r="25" spans="1:12">
-      <c r="A25" s="1" t="s">
+      <c r="A25" t="s">
         <v>112</v>
       </c>
       <c r="B25">
@@ -23887,7 +23861,7 @@
       </c>
     </row>
     <row r="26" spans="1:12">
-      <c r="A26" s="1" t="s">
+      <c r="A26" t="s">
         <v>113</v>
       </c>
       <c r="B26">
@@ -23919,7 +23893,7 @@
       </c>
     </row>
     <row r="27" spans="1:12">
-      <c r="A27" s="1" t="s">
+      <c r="A27" t="s">
         <v>114</v>
       </c>
       <c r="B27">
@@ -23945,12 +23919,12 @@
       </c>
     </row>
     <row r="28" spans="1:12">
-      <c r="A28" s="1" t="s">
+      <c r="A28" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="29" spans="1:12">
-      <c r="A29" s="1" t="s">
+      <c r="A29" t="s">
         <v>116</v>
       </c>
       <c r="B29">
@@ -23982,7 +23956,7 @@
       </c>
     </row>
     <row r="30" spans="1:12">
-      <c r="A30" s="1" t="s">
+      <c r="A30" t="s">
         <v>117</v>
       </c>
       <c r="B30">
@@ -24014,7 +23988,7 @@
       </c>
     </row>
     <row r="31" spans="1:12">
-      <c r="A31" s="1" t="s">
+      <c r="A31" t="s">
         <v>118</v>
       </c>
       <c r="B31">
@@ -24040,7 +24014,7 @@
       </c>
     </row>
     <row r="32" spans="1:12">
-      <c r="A32" s="1" t="s">
+      <c r="A32" t="s">
         <v>119</v>
       </c>
       <c r="B32">
@@ -24054,7 +24028,7 @@
       </c>
     </row>
     <row r="33" spans="1:12">
-      <c r="A33" s="1" t="s">
+      <c r="A33" t="s">
         <v>120</v>
       </c>
       <c r="B33">
@@ -24080,7 +24054,7 @@
       </c>
     </row>
     <row r="34" spans="1:12">
-      <c r="A34" s="1" t="s">
+      <c r="A34" t="s">
         <v>121</v>
       </c>
       <c r="B34">
@@ -24112,7 +24086,7 @@
       </c>
     </row>
     <row r="35" spans="1:12">
-      <c r="A35" s="1" t="s">
+      <c r="A35" t="s">
         <v>122</v>
       </c>
       <c r="B35">
@@ -24132,7 +24106,7 @@
       </c>
     </row>
     <row r="36" spans="1:12">
-      <c r="A36" s="1" t="s">
+      <c r="A36" t="s">
         <v>123</v>
       </c>
       <c r="B36">
@@ -24158,7 +24132,7 @@
       </c>
     </row>
     <row r="37" spans="1:12">
-      <c r="A37" s="1" t="s">
+      <c r="A37" t="s">
         <v>124</v>
       </c>
       <c r="B37">
@@ -24184,7 +24158,7 @@
       </c>
     </row>
     <row r="38" spans="1:12">
-      <c r="A38" s="1" t="s">
+      <c r="A38" t="s">
         <v>125</v>
       </c>
       <c r="B38">
@@ -24216,7 +24190,7 @@
       </c>
     </row>
     <row r="39" spans="1:12">
-      <c r="A39" s="1" t="s">
+      <c r="A39" t="s">
         <v>126</v>
       </c>
       <c r="B39">
@@ -24230,7 +24204,7 @@
       </c>
     </row>
     <row r="40" spans="1:12">
-      <c r="A40" s="1" t="s">
+      <c r="A40" t="s">
         <v>127</v>
       </c>
       <c r="B40">
@@ -24250,7 +24224,7 @@
       </c>
     </row>
     <row r="41" spans="1:12">
-      <c r="A41" s="1" t="s">
+      <c r="A41" t="s">
         <v>128</v>
       </c>
       <c r="B41">
@@ -24282,7 +24256,7 @@
       </c>
     </row>
     <row r="42" spans="1:12">
-      <c r="A42" s="1" t="s">
+      <c r="A42" t="s">
         <v>129</v>
       </c>
       <c r="B42">
@@ -24314,7 +24288,7 @@
       </c>
     </row>
     <row r="43" spans="1:12">
-      <c r="A43" s="1" t="s">
+      <c r="A43" t="s">
         <v>130</v>
       </c>
       <c r="B43">
@@ -24340,7 +24314,7 @@
       </c>
     </row>
     <row r="44" spans="1:12">
-      <c r="A44" s="1" t="s">
+      <c r="A44" t="s">
         <v>131</v>
       </c>
       <c r="B44">
@@ -24372,12 +24346,12 @@
       </c>
     </row>
     <row r="45" spans="1:12">
-      <c r="A45" s="1" t="s">
+      <c r="A45" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="46" spans="1:12">
-      <c r="A46" s="1" t="s">
+      <c r="A46" t="s">
         <v>133</v>
       </c>
       <c r="B46">
@@ -24409,12 +24383,12 @@
       </c>
     </row>
     <row r="47" spans="1:12">
-      <c r="A47" s="1" t="s">
+      <c r="A47" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="48" spans="1:12">
-      <c r="A48" s="1" t="s">
+      <c r="A48" t="s">
         <v>135</v>
       </c>
       <c r="B48">
@@ -24446,7 +24420,7 @@
       </c>
     </row>
     <row r="49" spans="1:12">
-      <c r="A49" s="1" t="s">
+      <c r="A49" t="s">
         <v>136</v>
       </c>
       <c r="B49">
@@ -24478,12 +24452,12 @@
       </c>
     </row>
     <row r="50" spans="1:12">
-      <c r="A50" s="1" t="s">
+      <c r="A50" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="51" spans="1:12">
-      <c r="A51" s="1" t="s">
+      <c r="A51" t="s">
         <v>138</v>
       </c>
       <c r="B51">
@@ -24509,7 +24483,7 @@
       </c>
     </row>
     <row r="52" spans="1:12">
-      <c r="A52" s="1" t="s">
+      <c r="A52" t="s">
         <v>139</v>
       </c>
       <c r="B52">
@@ -24535,7 +24509,7 @@
       </c>
     </row>
     <row r="53" spans="1:12">
-      <c r="A53" s="1" t="s">
+      <c r="A53" t="s">
         <v>140</v>
       </c>
       <c r="B53">
@@ -24571,45 +24545,45 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>38</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>46</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>78</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>79</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>80</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>81</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>89</v>
       </c>
       <c r="B2">
@@ -24641,7 +24615,7 @@
       </c>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>90</v>
       </c>
       <c r="B3">
@@ -24673,7 +24647,7 @@
       </c>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>91</v>
       </c>
       <c r="B4">
@@ -24705,7 +24679,7 @@
       </c>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>92</v>
       </c>
       <c r="B5">
@@ -24737,7 +24711,7 @@
       </c>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>93</v>
       </c>
       <c r="B6">
@@ -24769,7 +24743,7 @@
       </c>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>94</v>
       </c>
       <c r="B7">
@@ -24801,7 +24775,7 @@
       </c>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>95</v>
       </c>
       <c r="B8">
@@ -24833,7 +24807,7 @@
       </c>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>96</v>
       </c>
       <c r="B9">
@@ -24865,7 +24839,7 @@
       </c>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>97</v>
       </c>
       <c r="B10">
@@ -24897,7 +24871,7 @@
       </c>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>98</v>
       </c>
       <c r="B11">
@@ -24929,7 +24903,7 @@
       </c>
     </row>
     <row r="12" spans="1:12">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>99</v>
       </c>
       <c r="B12">
@@ -24961,7 +24935,7 @@
       </c>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>100</v>
       </c>
       <c r="B13">
@@ -24993,7 +24967,7 @@
       </c>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>101</v>
       </c>
       <c r="B14">
@@ -25025,7 +24999,7 @@
       </c>
     </row>
     <row r="15" spans="1:12">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>102</v>
       </c>
       <c r="B15">
@@ -25057,7 +25031,7 @@
       </c>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>103</v>
       </c>
       <c r="B16">
@@ -25089,7 +25063,7 @@
       </c>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>104</v>
       </c>
       <c r="B17">
@@ -25121,7 +25095,7 @@
       </c>
     </row>
     <row r="18" spans="1:12">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>105</v>
       </c>
       <c r="B18">
@@ -25153,7 +25127,7 @@
       </c>
     </row>
     <row r="19" spans="1:12">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>106</v>
       </c>
       <c r="B19">
@@ -25185,7 +25159,7 @@
       </c>
     </row>
     <row r="20" spans="1:12">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>107</v>
       </c>
       <c r="B20">
@@ -25217,7 +25191,7 @@
       </c>
     </row>
     <row r="21" spans="1:12">
-      <c r="A21" s="1" t="s">
+      <c r="A21" t="s">
         <v>108</v>
       </c>
       <c r="B21">
@@ -25249,7 +25223,7 @@
       </c>
     </row>
     <row r="22" spans="1:12">
-      <c r="A22" s="1" t="s">
+      <c r="A22" t="s">
         <v>109</v>
       </c>
       <c r="B22">
@@ -25281,7 +25255,7 @@
       </c>
     </row>
     <row r="23" spans="1:12">
-      <c r="A23" s="1" t="s">
+      <c r="A23" t="s">
         <v>110</v>
       </c>
       <c r="B23">
@@ -25313,7 +25287,7 @@
       </c>
     </row>
     <row r="24" spans="1:12">
-      <c r="A24" s="1" t="s">
+      <c r="A24" t="s">
         <v>111</v>
       </c>
       <c r="B24">
@@ -25345,7 +25319,7 @@
       </c>
     </row>
     <row r="25" spans="1:12">
-      <c r="A25" s="1" t="s">
+      <c r="A25" t="s">
         <v>112</v>
       </c>
       <c r="B25">
@@ -25377,7 +25351,7 @@
       </c>
     </row>
     <row r="26" spans="1:12">
-      <c r="A26" s="1" t="s">
+      <c r="A26" t="s">
         <v>113</v>
       </c>
       <c r="B26">
@@ -25409,7 +25383,7 @@
       </c>
     </row>
     <row r="27" spans="1:12">
-      <c r="A27" s="1" t="s">
+      <c r="A27" t="s">
         <v>114</v>
       </c>
       <c r="B27">
@@ -25441,7 +25415,7 @@
       </c>
     </row>
     <row r="28" spans="1:12">
-      <c r="A28" s="1" t="s">
+      <c r="A28" t="s">
         <v>115</v>
       </c>
       <c r="B28">
@@ -25473,7 +25447,7 @@
       </c>
     </row>
     <row r="29" spans="1:12">
-      <c r="A29" s="1" t="s">
+      <c r="A29" t="s">
         <v>116</v>
       </c>
       <c r="B29">
@@ -25505,7 +25479,7 @@
       </c>
     </row>
     <row r="30" spans="1:12">
-      <c r="A30" s="1" t="s">
+      <c r="A30" t="s">
         <v>117</v>
       </c>
       <c r="B30">
@@ -25537,7 +25511,7 @@
       </c>
     </row>
     <row r="31" spans="1:12">
-      <c r="A31" s="1" t="s">
+      <c r="A31" t="s">
         <v>118</v>
       </c>
       <c r="B31">
@@ -25569,7 +25543,7 @@
       </c>
     </row>
     <row r="32" spans="1:12">
-      <c r="A32" s="1" t="s">
+      <c r="A32" t="s">
         <v>119</v>
       </c>
       <c r="B32">
@@ -25601,7 +25575,7 @@
       </c>
     </row>
     <row r="33" spans="1:12">
-      <c r="A33" s="1" t="s">
+      <c r="A33" t="s">
         <v>120</v>
       </c>
       <c r="B33">
@@ -25633,7 +25607,7 @@
       </c>
     </row>
     <row r="34" spans="1:12">
-      <c r="A34" s="1" t="s">
+      <c r="A34" t="s">
         <v>121</v>
       </c>
       <c r="B34">
@@ -25665,7 +25639,7 @@
       </c>
     </row>
     <row r="35" spans="1:12">
-      <c r="A35" s="1" t="s">
+      <c r="A35" t="s">
         <v>122</v>
       </c>
       <c r="B35">
@@ -25697,7 +25671,7 @@
       </c>
     </row>
     <row r="36" spans="1:12">
-      <c r="A36" s="1" t="s">
+      <c r="A36" t="s">
         <v>123</v>
       </c>
       <c r="B36">
@@ -25729,7 +25703,7 @@
       </c>
     </row>
     <row r="37" spans="1:12">
-      <c r="A37" s="1" t="s">
+      <c r="A37" t="s">
         <v>124</v>
       </c>
       <c r="B37">
@@ -25761,7 +25735,7 @@
       </c>
     </row>
     <row r="38" spans="1:12">
-      <c r="A38" s="1" t="s">
+      <c r="A38" t="s">
         <v>125</v>
       </c>
       <c r="B38">
@@ -25793,7 +25767,7 @@
       </c>
     </row>
     <row r="39" spans="1:12">
-      <c r="A39" s="1" t="s">
+      <c r="A39" t="s">
         <v>126</v>
       </c>
       <c r="B39">
@@ -25825,7 +25799,7 @@
       </c>
     </row>
     <row r="40" spans="1:12">
-      <c r="A40" s="1" t="s">
+      <c r="A40" t="s">
         <v>127</v>
       </c>
       <c r="B40">
@@ -25857,7 +25831,7 @@
       </c>
     </row>
     <row r="41" spans="1:12">
-      <c r="A41" s="1" t="s">
+      <c r="A41" t="s">
         <v>128</v>
       </c>
       <c r="B41">
@@ -25889,7 +25863,7 @@
       </c>
     </row>
     <row r="42" spans="1:12">
-      <c r="A42" s="1" t="s">
+      <c r="A42" t="s">
         <v>129</v>
       </c>
       <c r="B42">
@@ -25921,7 +25895,7 @@
       </c>
     </row>
     <row r="43" spans="1:12">
-      <c r="A43" s="1" t="s">
+      <c r="A43" t="s">
         <v>130</v>
       </c>
       <c r="B43">
@@ -25953,7 +25927,7 @@
       </c>
     </row>
     <row r="44" spans="1:12">
-      <c r="A44" s="1" t="s">
+      <c r="A44" t="s">
         <v>131</v>
       </c>
       <c r="B44">
@@ -25985,7 +25959,7 @@
       </c>
     </row>
     <row r="45" spans="1:12">
-      <c r="A45" s="1" t="s">
+      <c r="A45" t="s">
         <v>132</v>
       </c>
       <c r="B45">
@@ -26017,7 +25991,7 @@
       </c>
     </row>
     <row r="46" spans="1:12">
-      <c r="A46" s="1" t="s">
+      <c r="A46" t="s">
         <v>133</v>
       </c>
       <c r="B46">
@@ -26049,7 +26023,7 @@
       </c>
     </row>
     <row r="47" spans="1:12">
-      <c r="A47" s="1" t="s">
+      <c r="A47" t="s">
         <v>134</v>
       </c>
       <c r="B47">
@@ -26081,7 +26055,7 @@
       </c>
     </row>
     <row r="48" spans="1:12">
-      <c r="A48" s="1" t="s">
+      <c r="A48" t="s">
         <v>135</v>
       </c>
       <c r="B48">
@@ -26113,7 +26087,7 @@
       </c>
     </row>
     <row r="49" spans="1:12">
-      <c r="A49" s="1" t="s">
+      <c r="A49" t="s">
         <v>136</v>
       </c>
       <c r="B49">
@@ -26145,7 +26119,7 @@
       </c>
     </row>
     <row r="50" spans="1:12">
-      <c r="A50" s="1" t="s">
+      <c r="A50" t="s">
         <v>137</v>
       </c>
       <c r="B50">
@@ -26177,7 +26151,7 @@
       </c>
     </row>
     <row r="51" spans="1:12">
-      <c r="A51" s="1" t="s">
+      <c r="A51" t="s">
         <v>138</v>
       </c>
       <c r="B51">
@@ -26209,7 +26183,7 @@
       </c>
     </row>
     <row r="52" spans="1:12">
-      <c r="A52" s="1" t="s">
+      <c r="A52" t="s">
         <v>139</v>
       </c>
       <c r="B52">
@@ -26241,7 +26215,7 @@
       </c>
     </row>
     <row r="53" spans="1:12">
-      <c r="A53" s="1" t="s">
+      <c r="A53" t="s">
         <v>140</v>
       </c>
       <c r="B53">
@@ -26283,45 +26257,45 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>39</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>47</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>83</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>84</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>85</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>86</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>89</v>
       </c>
       <c r="B2">
@@ -26353,7 +26327,7 @@
       </c>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>90</v>
       </c>
       <c r="B3">
@@ -26391,7 +26365,7 @@
       </c>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>91</v>
       </c>
       <c r="B4">
@@ -26429,7 +26403,7 @@
       </c>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>92</v>
       </c>
       <c r="B5">
@@ -26467,7 +26441,7 @@
       </c>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>93</v>
       </c>
       <c r="B6">
@@ -26505,7 +26479,7 @@
       </c>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>94</v>
       </c>
       <c r="B7">
@@ -26543,7 +26517,7 @@
       </c>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>95</v>
       </c>
       <c r="B8">
@@ -26581,7 +26555,7 @@
       </c>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>96</v>
       </c>
       <c r="B9">
@@ -26619,7 +26593,7 @@
       </c>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>97</v>
       </c>
       <c r="B10">
@@ -26657,7 +26631,7 @@
       </c>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>98</v>
       </c>
       <c r="B11">
@@ -26695,7 +26669,7 @@
       </c>
     </row>
     <row r="12" spans="1:12">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>99</v>
       </c>
       <c r="B12">
@@ -26733,7 +26707,7 @@
       </c>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>100</v>
       </c>
       <c r="B13">
@@ -26771,7 +26745,7 @@
       </c>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>101</v>
       </c>
       <c r="B14">
@@ -26809,7 +26783,7 @@
       </c>
     </row>
     <row r="15" spans="1:12">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>102</v>
       </c>
       <c r="B15">
@@ -26841,7 +26815,7 @@
       </c>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>103</v>
       </c>
       <c r="B16">
@@ -26879,7 +26853,7 @@
       </c>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>104</v>
       </c>
       <c r="B17">
@@ -26917,7 +26891,7 @@
       </c>
     </row>
     <row r="18" spans="1:12">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>105</v>
       </c>
       <c r="B18">
@@ -26955,7 +26929,7 @@
       </c>
     </row>
     <row r="19" spans="1:12">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>106</v>
       </c>
       <c r="B19">
@@ -26993,7 +26967,7 @@
       </c>
     </row>
     <row r="20" spans="1:12">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>107</v>
       </c>
       <c r="B20">
@@ -27031,7 +27005,7 @@
       </c>
     </row>
     <row r="21" spans="1:12">
-      <c r="A21" s="1" t="s">
+      <c r="A21" t="s">
         <v>108</v>
       </c>
       <c r="B21">
@@ -27069,7 +27043,7 @@
       </c>
     </row>
     <row r="22" spans="1:12">
-      <c r="A22" s="1" t="s">
+      <c r="A22" t="s">
         <v>109</v>
       </c>
       <c r="B22">
@@ -27107,7 +27081,7 @@
       </c>
     </row>
     <row r="23" spans="1:12">
-      <c r="A23" s="1" t="s">
+      <c r="A23" t="s">
         <v>110</v>
       </c>
       <c r="B23">
@@ -27145,7 +27119,7 @@
       </c>
     </row>
     <row r="24" spans="1:12">
-      <c r="A24" s="1" t="s">
+      <c r="A24" t="s">
         <v>111</v>
       </c>
       <c r="B24">
@@ -27183,7 +27157,7 @@
       </c>
     </row>
     <row r="25" spans="1:12">
-      <c r="A25" s="1" t="s">
+      <c r="A25" t="s">
         <v>112</v>
       </c>
       <c r="B25">
@@ -27221,7 +27195,7 @@
       </c>
     </row>
     <row r="26" spans="1:12">
-      <c r="A26" s="1" t="s">
+      <c r="A26" t="s">
         <v>113</v>
       </c>
       <c r="B26">
@@ -27259,7 +27233,7 @@
       </c>
     </row>
     <row r="27" spans="1:12">
-      <c r="A27" s="1" t="s">
+      <c r="A27" t="s">
         <v>114</v>
       </c>
       <c r="B27">
@@ -27297,7 +27271,7 @@
       </c>
     </row>
     <row r="28" spans="1:12">
-      <c r="A28" s="1" t="s">
+      <c r="A28" t="s">
         <v>115</v>
       </c>
       <c r="B28">
@@ -27329,7 +27303,7 @@
       </c>
     </row>
     <row r="29" spans="1:12">
-      <c r="A29" s="1" t="s">
+      <c r="A29" t="s">
         <v>116</v>
       </c>
       <c r="B29">
@@ -27367,7 +27341,7 @@
       </c>
     </row>
     <row r="30" spans="1:12">
-      <c r="A30" s="1" t="s">
+      <c r="A30" t="s">
         <v>117</v>
       </c>
       <c r="B30">
@@ -27405,7 +27379,7 @@
       </c>
     </row>
     <row r="31" spans="1:12">
-      <c r="A31" s="1" t="s">
+      <c r="A31" t="s">
         <v>118</v>
       </c>
       <c r="B31">
@@ -27443,7 +27417,7 @@
       </c>
     </row>
     <row r="32" spans="1:12">
-      <c r="A32" s="1" t="s">
+      <c r="A32" t="s">
         <v>119</v>
       </c>
       <c r="B32">
@@ -27481,7 +27455,7 @@
       </c>
     </row>
     <row r="33" spans="1:12">
-      <c r="A33" s="1" t="s">
+      <c r="A33" t="s">
         <v>120</v>
       </c>
       <c r="B33">
@@ -27519,7 +27493,7 @@
       </c>
     </row>
     <row r="34" spans="1:12">
-      <c r="A34" s="1" t="s">
+      <c r="A34" t="s">
         <v>121</v>
       </c>
       <c r="B34">
@@ -27557,7 +27531,7 @@
       </c>
     </row>
     <row r="35" spans="1:12">
-      <c r="A35" s="1" t="s">
+      <c r="A35" t="s">
         <v>122</v>
       </c>
       <c r="B35">
@@ -27595,7 +27569,7 @@
       </c>
     </row>
     <row r="36" spans="1:12">
-      <c r="A36" s="1" t="s">
+      <c r="A36" t="s">
         <v>123</v>
       </c>
       <c r="B36">
@@ -27633,7 +27607,7 @@
       </c>
     </row>
     <row r="37" spans="1:12">
-      <c r="A37" s="1" t="s">
+      <c r="A37" t="s">
         <v>124</v>
       </c>
       <c r="B37">
@@ -27671,7 +27645,7 @@
       </c>
     </row>
     <row r="38" spans="1:12">
-      <c r="A38" s="1" t="s">
+      <c r="A38" t="s">
         <v>125</v>
       </c>
       <c r="B38">
@@ -27709,7 +27683,7 @@
       </c>
     </row>
     <row r="39" spans="1:12">
-      <c r="A39" s="1" t="s">
+      <c r="A39" t="s">
         <v>126</v>
       </c>
       <c r="B39">
@@ -27747,7 +27721,7 @@
       </c>
     </row>
     <row r="40" spans="1:12">
-      <c r="A40" s="1" t="s">
+      <c r="A40" t="s">
         <v>127</v>
       </c>
       <c r="B40">
@@ -27785,7 +27759,7 @@
       </c>
     </row>
     <row r="41" spans="1:12">
-      <c r="A41" s="1" t="s">
+      <c r="A41" t="s">
         <v>128</v>
       </c>
       <c r="B41">
@@ -27823,7 +27797,7 @@
       </c>
     </row>
     <row r="42" spans="1:12">
-      <c r="A42" s="1" t="s">
+      <c r="A42" t="s">
         <v>129</v>
       </c>
       <c r="B42">
@@ -27861,7 +27835,7 @@
       </c>
     </row>
     <row r="43" spans="1:12">
-      <c r="A43" s="1" t="s">
+      <c r="A43" t="s">
         <v>130</v>
       </c>
       <c r="B43">
@@ -27899,7 +27873,7 @@
       </c>
     </row>
     <row r="44" spans="1:12">
-      <c r="A44" s="1" t="s">
+      <c r="A44" t="s">
         <v>131</v>
       </c>
       <c r="B44">
@@ -27937,7 +27911,7 @@
       </c>
     </row>
     <row r="45" spans="1:12">
-      <c r="A45" s="1" t="s">
+      <c r="A45" t="s">
         <v>132</v>
       </c>
       <c r="B45">
@@ -27969,7 +27943,7 @@
       </c>
     </row>
     <row r="46" spans="1:12">
-      <c r="A46" s="1" t="s">
+      <c r="A46" t="s">
         <v>133</v>
       </c>
       <c r="B46">
@@ -28007,7 +27981,7 @@
       </c>
     </row>
     <row r="47" spans="1:12">
-      <c r="A47" s="1" t="s">
+      <c r="A47" t="s">
         <v>134</v>
       </c>
       <c r="B47">
@@ -28039,7 +28013,7 @@
       </c>
     </row>
     <row r="48" spans="1:12">
-      <c r="A48" s="1" t="s">
+      <c r="A48" t="s">
         <v>135</v>
       </c>
       <c r="B48">
@@ -28077,7 +28051,7 @@
       </c>
     </row>
     <row r="49" spans="1:12">
-      <c r="A49" s="1" t="s">
+      <c r="A49" t="s">
         <v>136</v>
       </c>
       <c r="B49">
@@ -28115,7 +28089,7 @@
       </c>
     </row>
     <row r="50" spans="1:12">
-      <c r="A50" s="1" t="s">
+      <c r="A50" t="s">
         <v>137</v>
       </c>
       <c r="B50">
@@ -28147,7 +28121,7 @@
       </c>
     </row>
     <row r="51" spans="1:12">
-      <c r="A51" s="1" t="s">
+      <c r="A51" t="s">
         <v>138</v>
       </c>
       <c r="B51">
@@ -28185,7 +28159,7 @@
       </c>
     </row>
     <row r="52" spans="1:12">
-      <c r="A52" s="1" t="s">
+      <c r="A52" t="s">
         <v>139</v>
       </c>
       <c r="B52">
@@ -28217,7 +28191,7 @@
       </c>
     </row>
     <row r="53" spans="1:12">
-      <c r="A53" s="1" t="s">
+      <c r="A53" t="s">
         <v>140</v>
       </c>
       <c r="B53">
